--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfo.xlsx
@@ -16,22 +16,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
-    <t>退款单号</t>
-  </si>
-  <si>
-    <t>平台订单编号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>退款金额</t>
+    <t>*退款单号</t>
+  </si>
+  <si>
+    <t>*平台订单编号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*退款金额</t>
   </si>
   <si>
     <t>汇率</t>
@@ -40,16 +40,16 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>退款数量</t>
-  </si>
-  <si>
-    <t>退款状态</t>
-  </si>
-  <si>
-    <t>退款时间</t>
-  </si>
-  <si>
-    <t>原订单时间</t>
+    <t>*退款数量</t>
+  </si>
+  <si>
+    <t>*退款状态</t>
+  </si>
+  <si>
+    <t>*退款时间</t>
+  </si>
+  <si>
+    <t>*币种</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -88,7 +88,7 @@
     <t>{.refundTime}</t>
   </si>
   <si>
-    <t>{.orderTime}</t>
+    <t>{.currencyCode}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1152,10 +1152,25 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="5">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576 H2:H1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"新建退款,审核中,财务审核,成功,失败,作废"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfo.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfo.xlsx
@@ -55,7 +55,7 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.refundId}</t>
+    <t>{.refundCode}</t>
   </si>
   <si>
     <t>{.platformOrderId}</t>
@@ -1161,9 +1161,6 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>"新建退款,审核中,财务审核,成功,失败,作废"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
@@ -1172,6 +1169,9 @@
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"新建退款,审核中,财务审核,成功,失败,作废"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
